--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488190_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488190_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7504</v>
+        <v>5.5809</v>
       </c>
       <c r="E2" t="n">
-        <v>5.7223</v>
+        <v>5.2327</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0281</v>
+        <v>0.3482</v>
       </c>
       <c r="G2" t="n">
         <v>3.9398</v>
@@ -610,13 +610,13 @@
         <v>1.297</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3067</v>
+        <v>0.1371</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2114</v>
+        <v>-0.2782</v>
       </c>
       <c r="U2" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.4153</v>
       </c>
       <c r="V2" t="n">
         <v>1.1334</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.617</v>
+        <v>4.9349</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2244</v>
+        <v>5.6161</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6073</v>
+        <v>-0.6812</v>
       </c>
       <c r="G3" t="n">
         <v>2.2593</v>
@@ -688,13 +688,13 @@
         <v>1.8529</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3315</v>
+        <v>-0.0137</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9849</v>
+        <v>-0.5931</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6533</v>
+        <v>0.5795</v>
       </c>
       <c r="V3" t="n">
         <v>1.7628</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9205</v>
+        <v>3.0632</v>
       </c>
       <c r="E4" t="n">
-        <v>3.32</v>
+        <v>2.5366</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6005</v>
+        <v>0.5266</v>
       </c>
       <c r="G4" t="n">
         <v>-0.2096</v>
@@ -766,13 +766,13 @@
         <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6818</v>
+        <v>0.8245</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7549</v>
+        <v>-0.0286</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.853</v>
       </c>
       <c r="V4" t="n">
         <v>2.0778</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7721</v>
+        <v>0.7726</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0094</v>
+        <v>-1.1074</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7815</v>
+        <v>1.88</v>
       </c>
       <c r="G5" t="n">
         <v>0.4963</v>
@@ -844,13 +844,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4574</v>
+        <v>0.4579</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1057</v>
+        <v>0.0078</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3517</v>
+        <v>0.4501</v>
       </c>
       <c r="V5" t="n">
         <v>0.189</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4306</v>
+        <v>0.5543</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8397</v>
+        <v>2.7418</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.4091</v>
+        <v>-2.1875</v>
       </c>
       <c r="G6" t="n">
         <v>0.0806</v>
@@ -922,13 +922,13 @@
         <v>1.6676</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2477</v>
+        <v>-0.124</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5508999999999999</v>
+        <v>-0.6488</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3032</v>
+        <v>0.5248</v>
       </c>
       <c r="V6" t="n">
         <v>-1.0699</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="E8" t="n">
         <v>-0.0547</v>
       </c>
       <c r="F8" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="G8" t="n">
         <v>0.1306</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0383</v>
+        <v>-0.0137</v>
       </c>
       <c r="T8" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0164</v>
+        <v>0.041</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>A. MENDEZ CARRION</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4559</v>
+        <v>-0.1989</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4673</v>
+        <v>0.3598</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0114</v>
+        <v>-0.5587</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4052</v>
+        <v>-1.734</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8983</v>
+        <v>-0.9198</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4931</v>
+        <v>-0.8142</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3996</v>
+        <v>1.0858</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.524</v>
+        <v>1.5929</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1244</v>
+        <v>-0.5071</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0056</v>
+        <v>-2.8198</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3743</v>
+        <v>-2.5127</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3687</v>
+        <v>-0.3071</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.7411</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5558999999999999</v>
+        <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0234</v>
+        <v>-0.1505</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4377</v>
+        <v>-0.429</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4611</v>
+        <v>0.2785</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.63</v>
+        <v>0.9444</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.63</v>
+        <v>0.6294</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LEIRO</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5011</v>
+        <v>-0.3099</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8094</v>
+        <v>-1.1735</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3083</v>
+        <v>0.8637</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8319</v>
+        <v>-0.4052</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0039</v>
+        <v>-0.8983</v>
       </c>
       <c r="I10" t="n">
-        <v>0.172</v>
+        <v>0.4931</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1488</v>
+        <v>-0.3996</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1074</v>
+        <v>-0.524</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0415</v>
+        <v>0.1244</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9807</v>
+        <v>-0.0056</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1113</v>
+        <v>-0.3743</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1306</v>
+        <v>0.3687</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0343</v>
+        <v>0.1694</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3283</v>
+        <v>-0.1439</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3626</v>
+        <v>0.3134</v>
       </c>
       <c r="V10" t="n">
         <v>-0.63</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MENDEZ CARRION</t>
+          <t>A. RODRIGUEZ LEIRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6645</v>
+        <v>-0.6986</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0319</v>
+        <v>-0.7115</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.0129</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.734</v>
+        <v>-0.8319</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9198</v>
+        <v>-1.0039</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8142</v>
+        <v>0.172</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0858</v>
+        <v>0.1488</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5929</v>
+        <v>0.1074</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5071</v>
+        <v>0.0415</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.8198</v>
+        <v>-0.9807</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5127</v>
+        <v>-1.1113</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3071</v>
+        <v>0.1306</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.616</v>
+        <v>-0.1632</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8207</v>
+        <v>-0.2304</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2047</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>0.9444</v>
+        <v>-0.63</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6294</v>
+        <v>-0.63</v>
       </c>
       <c r="X11" t="n">
-        <v>0.315</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>J. PAREDES BERMEJO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0037</v>
+        <v>-2.1484</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0376</v>
+        <v>0.1028</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0413</v>
+        <v>-2.2512</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6868</v>
+        <v>-1.1529</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4149</v>
+        <v>-1.2633</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2718</v>
+        <v>0.1105</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6564</v>
+        <v>0.3878</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8163</v>
+        <v>0.408</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8401</v>
+        <v>-0.0201</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.9697</v>
+        <v>-1.5407</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4014</v>
+        <v>-1.6713</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5683</v>
+        <v>0.1306</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8529</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.7793</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9264</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7357</v>
+        <v>-0.2925</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1604</v>
+        <v>-0.2851</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5752</v>
+        <v>-0.0075</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.5733</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. PAREDES BERMEJO</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3202</v>
+        <v>-2.3719</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0048</v>
+        <v>-0.1583</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.325</v>
+        <v>-2.2136</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.1529</v>
+        <v>0.6868</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2633</v>
+        <v>0.4149</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1105</v>
+        <v>0.2718</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3878</v>
+        <v>2.6564</v>
       </c>
       <c r="K13" t="n">
-        <v>0.408</v>
+        <v>1.8163</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0201</v>
+        <v>0.8401</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5407</v>
+        <v>-1.9697</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6713</v>
+        <v>-1.4014</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1306</v>
+        <v>-0.5683</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.7793</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.9264</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4643</v>
+        <v>0.3675</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.383</v>
+        <v>-0.0354</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0813</v>
+        <v>0.4029</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2589</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.7411</v>
+        <v>-2.3986</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.7528</v>
+        <v>-3.3611</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0118</v>
+        <v>0.9625</v>
       </c>
       <c r="G14" t="n">
         <v>-1.499</v>
@@ -1546,13 +1546,13 @@
         <v>0.7411</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1298</v>
+        <v>0.2126</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.383</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2532</v>
+        <v>0.2039</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0005</v>
@@ -1579,7 +1579,7 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.218500000000001</v>
+        <v>7.218599999999995</v>
       </c>
       <c r="E15" t="n">
         <v>10.3454</v>
@@ -1588,7 +1588,7 @@
         <v>-3.1267</v>
       </c>
       <c r="G15" t="n">
-        <v>2.082899999999999</v>
+        <v>2.0829</v>
       </c>
       <c r="H15" t="n">
         <v>-5.1357</v>
@@ -1624,16 +1624,16 @@
         <v>12.0437</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4117</v>
+        <v>1.4114</v>
       </c>
       <c r="T15" t="n">
-        <v>-2.7108</v>
+        <v>-2.7107</v>
       </c>
       <c r="U15" t="n">
-        <v>4.122199999999999</v>
+        <v>4.122</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9448000000000003</v>
+        <v>0.9448000000000012</v>
       </c>
       <c r="W15" t="n">
         <v>3.774999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.77</v>
+        <v>6.1136</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4154</v>
+        <v>7.6113</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6455</v>
+        <v>-1.4977</v>
       </c>
       <c r="G16" t="n">
         <v>4.432</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7732</v>
+        <v>-0.4296</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.766</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0072</v>
+        <v>0.1405</v>
       </c>
       <c r="V16" t="n">
         <v>0.6289</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.3492</v>
+        <v>2.7622</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2402</v>
+        <v>1.5547</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1089</v>
+        <v>1.2074</v>
       </c>
       <c r="G17" t="n">
         <v>3.5342</v>
@@ -1780,13 +1780,13 @@
         <v>0.3706</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0008</v>
+        <v>0.4138</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6491</v>
+        <v>-0.0364</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3517</v>
+        <v>0.4501</v>
       </c>
       <c r="V17" t="n">
         <v>-0.63</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2259</v>
+        <v>-0.2505</v>
       </c>
       <c r="E20" t="n">
         <v>-0.2306</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0047</v>
+        <v>-0.0199</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0789</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.147</v>
+        <v>-0.1716</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2736</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1266</v>
+        <v>0.102</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>D. ESCAMILLA DE SANTOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3839</v>
+        <v>-0.8207</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3751</v>
+        <v>0.1732</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.759</v>
+        <v>-0.9939</v>
       </c>
       <c r="G21" t="n">
-        <v>0.97</v>
+        <v>-1.167</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3031</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3331</v>
+        <v>-1.0951</v>
       </c>
       <c r="J21" t="n">
-        <v>5.126</v>
+        <v>0.6339</v>
       </c>
       <c r="K21" t="n">
-        <v>5.6852</v>
+        <v>1.2453</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5592</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.1559</v>
+        <v>-1.801</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.3821</v>
+        <v>-1.3173</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7738</v>
+        <v>-0.4837</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3706</v>
+        <v>1.1117</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4823</v>
+        <v>1.1117</v>
       </c>
       <c r="S21" t="n">
-        <v>1.5338</v>
+        <v>-0.7654</v>
       </c>
       <c r="T21" t="n">
-        <v>0.102</v>
+        <v>-0.4607</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4318</v>
+        <v>-0.3047</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.5172</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.5172</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. ESCAMILLA DE SANTOS</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1397</v>
+        <v>-1.0257</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0226</v>
+        <v>-1.1632</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.117</v>
+        <v>0.1375</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.167</v>
+        <v>-1.5921</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-2.222</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.0951</v>
+        <v>0.6299</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6339</v>
+        <v>-0.8119</v>
       </c>
       <c r="K22" t="n">
-        <v>1.2453</v>
+        <v>-0.8119</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6114000000000001</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.801</v>
+        <v>-0.7803</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3173</v>
+        <v>-1.4101</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4837</v>
+        <v>0.6299</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0844</v>
+        <v>-0.1747</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6566</v>
+        <v>-0.3513</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4278</v>
+        <v>0.1766</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1507</v>
+        <v>-1.6179</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5495</v>
+        <v>-0.6474</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6011</v>
+        <v>-0.9705</v>
       </c>
       <c r="G23" t="n">
         <v>-4.8341</v>
@@ -2248,13 +2248,13 @@
         <v>1.1117</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6839</v>
+        <v>0.2167</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.332</v>
+        <v>-0.4299</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0159</v>
+        <v>0.6466</v>
       </c>
       <c r="V23" t="n">
         <v>1.8877</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>C. SAENZ - DIAZ MURO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3201</v>
+        <v>-1.664</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.359</v>
+        <v>-1.0906</v>
       </c>
       <c r="F24" t="n">
-        <v>0.039</v>
+        <v>-0.5735</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.5921</v>
+        <v>-0.1219</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.222</v>
+        <v>-0.383</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6299</v>
+        <v>0.2611</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.8119</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8119</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7803</v>
+        <v>-0.1219</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4101</v>
+        <v>-0.383</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6299</v>
+        <v>0.2611</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7411</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R24" t="n">
-        <v>0.7411</v>
+        <v>0.1853</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4691</v>
+        <v>-0.1716</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5471</v>
+        <v>-0.1641</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0781</v>
+        <v>-0.0075</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C. SAENZ - DIAZ MURO</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7379</v>
+        <v>-1.7337</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.0906</v>
+        <v>2.5917</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6473</v>
+        <v>-4.3253</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1219</v>
+        <v>0.97</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.383</v>
+        <v>3.3031</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2611</v>
+        <v>-2.3331</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>5.126</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>5.6852</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-0.5592</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1219</v>
+        <v>-4.1559</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.383</v>
+        <v>-2.3821</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2611</v>
+        <v>-1.7738</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7411</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R25" t="n">
-        <v>0.1853</v>
+        <v>1.4823</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2455</v>
+        <v>0.184</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1641</v>
+        <v>-0.6814</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0813</v>
+        <v>0.8655</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6294</v>
+        <v>-2.5172</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6294</v>
+        <v>-2.5172</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>M. PARRA JIMENEZ</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.1144</v>
+        <v>-1.8674</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.7403</v>
+        <v>-0.3133</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6259</v>
+        <v>-1.5541</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.51</v>
+        <v>0.1088</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9877</v>
+        <v>0.5281</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5223</v>
+        <v>-0.4192</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.8727</v>
+        <v>1.2049</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.5669999999999999</v>
+        <v>1.1635</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3057</v>
+        <v>0.0415</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3627</v>
+        <v>-1.0961</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4207</v>
+        <v>-0.6354</v>
       </c>
       <c r="O26" t="n">
-        <v>0.7834</v>
+        <v>-0.4607</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.4823</v>
+        <v>-1.297</v>
       </c>
       <c r="Q26" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3706</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2484</v>
+        <v>0.2652</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2736</v>
+        <v>0.0202</v>
       </c>
       <c r="U26" t="n">
-        <v>0.522</v>
+        <v>0.245</v>
       </c>
       <c r="V26" t="n">
-        <v>0.6294</v>
+        <v>-0.9444</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2589</v>
+        <v>0.3144</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.6294</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>M. PARRA JIMENEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.1366</v>
+        <v>-2.0914</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6071</v>
+        <v>-2.4465</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5295</v>
+        <v>0.3551</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1088</v>
+        <v>-1.51</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5281</v>
+        <v>-0.9877</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.4192</v>
+        <v>-0.5223</v>
       </c>
       <c r="J27" t="n">
-        <v>1.2049</v>
+        <v>-1.8727</v>
       </c>
       <c r="K27" t="n">
-        <v>1.1635</v>
+        <v>-0.5669999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0415</v>
+        <v>-1.3057</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.0961</v>
+        <v>0.3627</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.6354</v>
+        <v>-0.4207</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.4607</v>
+        <v>0.7834</v>
       </c>
       <c r="P27" t="n">
-        <v>-1.297</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q27" t="n">
         <v>-1.8529</v>
       </c>
       <c r="R27" t="n">
-        <v>0.5558999999999999</v>
+        <v>0.3706</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.004</v>
+        <v>0.2714</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.2736</v>
+        <v>0.0202</v>
       </c>
       <c r="U27" t="n">
-        <v>0.2696</v>
+        <v>0.2512</v>
       </c>
       <c r="V27" t="n">
-        <v>-0.9444</v>
+        <v>0.6294</v>
       </c>
       <c r="W27" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X27" t="n">
-        <v>-1.2589</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.1918</v>
+        <v>-2.6758</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.0949</v>
+        <v>-2.899</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0969</v>
+        <v>0.2232</v>
       </c>
       <c r="G28" t="n">
         <v>-3.2269</v>
@@ -2638,13 +2638,13 @@
         <v>0.3706</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.9655</v>
+        <v>-0.4495</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.6566</v>
+        <v>-0.4607</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.3089</v>
+        <v>0.0112</v>
       </c>
       <c r="V28" t="n">
         <v>0.63</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-4.203</v>
+        <v>-3.6132</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4757</v>
+        <v>-1.2798</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.7273</v>
+        <v>-2.3334</v>
       </c>
       <c r="G29" t="n">
         <v>0.1367</v>
@@ -2716,13 +2716,13 @@
         <v>1.4823</v>
       </c>
       <c r="S29" t="n">
-        <v>-1.1898</v>
+        <v>-0.6</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.9302</v>
+        <v>-0.7343</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.2597</v>
+        <v>0.1343</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,10 +2749,10 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-7.218600000000001</v>
+        <v>-7.218300000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>3.1266</v>
+        <v>3.126699999999999</v>
       </c>
       <c r="F30" t="n">
         <v>-10.3451</v>
@@ -2764,7 +2764,7 @@
         <v>5.1357</v>
       </c>
       <c r="I30" t="n">
-        <v>-7.218500000000001</v>
+        <v>-7.2185</v>
       </c>
       <c r="J30" t="n">
         <v>16.4625</v>
@@ -2791,13 +2791,13 @@
         <v>-12.0437</v>
       </c>
       <c r="R30" t="n">
-        <v>9.2644</v>
+        <v>9.264399999999998</v>
       </c>
       <c r="S30" t="n">
-        <v>-1.4116</v>
+        <v>-1.4113</v>
       </c>
       <c r="T30" t="n">
-        <v>-4.1223</v>
+        <v>-4.1221</v>
       </c>
       <c r="U30" t="n">
         <v>2.7108</v>
